--- a/Outputs/Scenarios/PtX_demand_CY_Ammonia.xlsx
+++ b/Outputs/Scenarios/PtX_demand_CY_Ammonia.xlsx
@@ -1037,7 +1037,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0007576705983832278</v>
+        <v>0.0008210627489166696</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.0001704505912360756</v>
       </c>
     </row>
     <row r="18">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.001515341196766456</v>
+        <v>0.001363604729888605</v>
       </c>
     </row>
     <row r="20">
@@ -1481,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0002525568661277426</v>
+        <v>0.0001704505912360756</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.004089523146886639</v>
+        <v>0.00443168195242908</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.0009200061870526381</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.008179046293773277</v>
+        <v>0.007360049496421105</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.001363174382295546</v>
+        <v>0.0009200061870526381</v>
       </c>
     </row>
     <row r="43">
